--- a/workflows/travel-reimbursement-form/templates/travel-expense-report.xlsx
+++ b/workflows/travel-reimbursement-form/templates/travel-expense-report.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="Kategorier">Sheet2!$A$1:$A$7</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
